--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lineaalimentos.sharepoint.com/sites/PlanejamentoSOP2/Documentos Compartilhados/BD/Cadastro/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{E9D71520-CE73-441D-B72A-13159F17FC6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25E23A78-AD42-449C-A7F6-061D2D9982D8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C2A970-5211-4CFE-974A-DB73F2750ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4763,7 +4763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4781,10 +4781,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -5265,7 +5264,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I489" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41">
-  <autoFilter ref="A1:I489" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I489">
     <sortCondition ref="A1:A489"/>
   </sortState>
@@ -6622,7 +6620,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
+      <c r="A35">
         <v>410022034</v>
       </c>
       <c r="B35" t="s">
@@ -13631,7 +13629,7 @@
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A277" s="8">
+      <c r="A277">
         <v>412066306</v>
       </c>
       <c r="B277" t="s">
@@ -13660,7 +13658,7 @@
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A278" s="8">
+      <c r="A278">
         <v>412283981</v>
       </c>
       <c r="B278" t="s">
@@ -13689,7 +13687,7 @@
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A279" s="8">
+      <c r="A279">
         <v>412284081</v>
       </c>
       <c r="B279" t="s">
@@ -13718,7 +13716,7 @@
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A280" s="8">
+      <c r="A280">
         <v>413440244</v>
       </c>
       <c r="B280" t="s">
@@ -13747,7 +13745,7 @@
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A281" s="8">
+      <c r="A281">
         <v>413450245</v>
       </c>
       <c r="B281" t="s">
@@ -13776,7 +13774,7 @@
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A282" s="8">
+      <c r="A282">
         <v>413450445</v>
       </c>
       <c r="B282" t="s">
@@ -13805,7 +13803,7 @@
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A283" s="8">
+      <c r="A283">
         <v>413456745</v>
       </c>
       <c r="B283" t="s">
@@ -14124,7 +14122,7 @@
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A294" s="8">
+      <c r="A294">
         <v>415025653</v>
       </c>
       <c r="B294" t="s">
@@ -14298,7 +14296,7 @@
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A300" s="9">
+      <c r="A300" s="8">
         <v>418025614</v>
       </c>
       <c r="B300" t="s">
@@ -14369,7 +14367,7 @@
         <v>73</v>
       </c>
       <c r="E302" t="s">
-        <v>16</v>
+        <v>1552</v>
       </c>
       <c r="F302" t="s">
         <v>11</v>
@@ -19722,38 +19720,38 @@
     <cfRule type="duplicateValues" dxfId="24" priority="32"/>
     <cfRule type="duplicateValues" dxfId="23" priority="33"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A489">
+    <cfRule type="duplicateValues" dxfId="22" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="108"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A330">
-    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A332">
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A333">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A335:A489">
-    <cfRule type="duplicateValues" dxfId="4" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="68"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A489">
-    <cfRule type="duplicateValues" dxfId="1" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -37686,18 +37684,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37719,18 +37717,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C2A970-5211-4CFE-974A-DB73F2750ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177FD10B-B226-4AB5-B1B9-E9D185CEA54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6778" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6786" uniqueCount="1560">
   <si>
     <t>PRODUTO</t>
   </si>
@@ -4763,7 +4763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4787,12 +4787,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan1" xfId="1" xr:uid="{FE852428-3A3C-4AA6-BBE1-A060037A7EA3}"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="45">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5263,27 +5285,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I489" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I490" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I489">
     <sortCondition ref="A1:A489"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="A1:C1272" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E944E400-526F-434F-B83C-CFB22E9A80C5}" name="COD PRODUTO"/>
@@ -5295,12 +5317,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A1:C350" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5623,7 +5645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I489"/>
+  <dimension ref="A1:I490"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -19715,43 +19737,72 @@
         <v>11</v>
       </c>
     </row>
+    <row r="490" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A490" s="9">
+        <v>1</v>
+      </c>
+      <c r="B490" t="s">
+        <v>19</v>
+      </c>
+      <c r="C490" t="s">
+        <v>26</v>
+      </c>
+      <c r="D490" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E490" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F490" t="s">
+        <v>11</v>
+      </c>
+      <c r="G490" t="s">
+        <v>11</v>
+      </c>
+      <c r="H490" t="s">
+        <v>11</v>
+      </c>
+      <c r="I490" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A489">
-    <cfRule type="duplicateValues" dxfId="22" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="108"/>
+  <conditionalFormatting sqref="A2:A490">
+    <cfRule type="duplicateValues" dxfId="24" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A330">
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A332">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A333">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A335:A489">
-    <cfRule type="duplicateValues" dxfId="2" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="68"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -37684,18 +37735,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37717,18 +37768,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{177FD10B-B226-4AB5-B1B9-E9D185CEA54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905A943B-C0BD-4E9B-AD0E-3EB2ECFDB6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4763,7 +4763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4787,34 +4787,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan1" xfId="1" xr:uid="{FE852428-3A3C-4AA6-BBE1-A060037A7EA3}"/>
   </cellStyles>
-  <dxfs count="45">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="43">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5285,27 +5263,27 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I490" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I490" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I489">
     <sortCondition ref="A1:A489"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="30">
   <autoFilter ref="A1:C1272" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E944E400-526F-434F-B83C-CFB22E9A80C5}" name="COD PRODUTO"/>
@@ -5317,12 +5295,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
   <autoFilter ref="A1:C350" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14328,7 +14306,7 @@
         <v>9</v>
       </c>
       <c r="D300" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E300" t="s">
         <v>16</v>
@@ -19738,7 +19716,7 @@
       </c>
     </row>
     <row r="490" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A490" s="9">
+      <c r="A490">
         <v>1</v>
       </c>
       <c r="B490" t="s">
@@ -19747,10 +19725,10 @@
       <c r="C490" t="s">
         <v>26</v>
       </c>
-      <c r="D490" s="9" t="s">
+      <c r="D490" t="s">
         <v>27</v>
       </c>
-      <c r="E490" s="10" t="s">
+      <c r="E490" t="s">
         <v>16</v>
       </c>
       <c r="F490" t="s">
@@ -19768,41 +19746,41 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A490">
-    <cfRule type="duplicateValues" dxfId="24" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A330">
-    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A332">
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A333">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A335:A489">
-    <cfRule type="duplicateValues" dxfId="4" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -37597,6 +37575,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010077ADB75EDE6CA24D9907F62E3498CFFE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9e4a933615ec58deeded07da77faa5c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f6c80a7e-4993-4462-a012-3c1269aac47c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dfd25e57b156fdb3c6d899fc66d2ed42" ns2:_="">
     <xsd:import namespace="f6c80a7e-4993-4462-a012-3c1269aac47c"/>
@@ -37734,22 +37727,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F883CBD-C14F-4597-A1B4-21AD70EB2EF7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37765,21 +37760,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905A943B-C0BD-4E9B-AD0E-3EB2ECFDB6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F380FC-5E11-4801-9DEE-B3A4C4E7855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5626,7 +5626,7 @@
   <dimension ref="A1:I490"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="35" bestFit="1" customWidth="1"/>
@@ -8077,7 +8077,7 @@
         <v>38</v>
       </c>
       <c r="E85" t="s">
-        <v>1555</v>
+        <v>11</v>
       </c>
       <c r="F85" t="s">
         <v>55</v>
@@ -8138,7 +8138,7 @@
         <v>1556</v>
       </c>
       <c r="F87" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="G87" t="s">
         <v>16</v>
@@ -8193,7 +8193,7 @@
         <v>38</v>
       </c>
       <c r="E89" t="s">
-        <v>1555</v>
+        <v>11</v>
       </c>
       <c r="F89" t="s">
         <v>39</v>
@@ -8251,7 +8251,7 @@
         <v>38</v>
       </c>
       <c r="E91" t="s">
-        <v>1552</v>
+        <v>11</v>
       </c>
       <c r="F91" t="s">
         <v>39</v>
@@ -8280,7 +8280,7 @@
         <v>38</v>
       </c>
       <c r="E92" t="s">
-        <v>1552</v>
+        <v>11</v>
       </c>
       <c r="F92" t="s">
         <v>39</v>
@@ -8309,7 +8309,7 @@
         <v>38</v>
       </c>
       <c r="E93" t="s">
-        <v>1555</v>
+        <v>11</v>
       </c>
       <c r="F93" t="s">
         <v>55</v>
@@ -8338,7 +8338,7 @@
         <v>38</v>
       </c>
       <c r="E94" t="s">
-        <v>1555</v>
+        <v>11</v>
       </c>
       <c r="F94" t="s">
         <v>55</v>
@@ -8367,7 +8367,7 @@
         <v>38</v>
       </c>
       <c r="E95" t="s">
-        <v>1555</v>
+        <v>11</v>
       </c>
       <c r="F95" t="s">
         <v>55</v>
@@ -8396,7 +8396,7 @@
         <v>38</v>
       </c>
       <c r="E96" t="s">
-        <v>1556</v>
+        <v>11</v>
       </c>
       <c r="F96" t="s">
         <v>39</v>
@@ -8425,7 +8425,7 @@
         <v>38</v>
       </c>
       <c r="E97" t="s">
-        <v>1552</v>
+        <v>11</v>
       </c>
       <c r="F97" t="s">
         <v>16</v>
@@ -8454,7 +8454,7 @@
         <v>38</v>
       </c>
       <c r="E98" t="s">
-        <v>1552</v>
+        <v>11</v>
       </c>
       <c r="F98" t="s">
         <v>16</v>
@@ -8483,7 +8483,7 @@
         <v>38</v>
       </c>
       <c r="E99" t="s">
-        <v>1552</v>
+        <v>11</v>
       </c>
       <c r="F99" t="s">
         <v>16</v>
@@ -10249,7 +10249,7 @@
         <v>37</v>
       </c>
       <c r="E160" t="s">
-        <v>1552</v>
+        <v>11</v>
       </c>
       <c r="F160" t="s">
         <v>16</v>
@@ -10452,7 +10452,7 @@
         <v>37</v>
       </c>
       <c r="E167" t="s">
-        <v>1552</v>
+        <v>11</v>
       </c>
       <c r="F167" t="s">
         <v>16</v>
@@ -14222,7 +14222,7 @@
         <v>17</v>
       </c>
       <c r="E297" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F297" t="s">
         <v>11</v>
@@ -14251,7 +14251,7 @@
         <v>13</v>
       </c>
       <c r="E298" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F298" t="s">
         <v>11</v>
@@ -14280,7 +14280,7 @@
         <v>36</v>
       </c>
       <c r="E299" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F299" t="s">
         <v>11</v>
@@ -14309,7 +14309,7 @@
         <v>10</v>
       </c>
       <c r="E300" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F300" t="s">
         <v>11</v>
@@ -14338,7 +14338,7 @@
         <v>18</v>
       </c>
       <c r="E301" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F301" t="s">
         <v>11</v>
@@ -37584,12 +37584,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010077ADB75EDE6CA24D9907F62E3498CFFE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9e4a933615ec58deeded07da77faa5c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f6c80a7e-4993-4462-a012-3c1269aac47c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dfd25e57b156fdb3c6d899fc66d2ed42" ns2:_="">
     <xsd:import namespace="f6c80a7e-4993-4462-a012-3c1269aac47c"/>
@@ -37727,6 +37721,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
   <ds:schemaRefs>
@@ -37736,15 +37736,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F883CBD-C14F-4597-A1B4-21AD70EB2EF7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37760,4 +37751,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F380FC-5E11-4801-9DEE-B3A4C4E7855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2D5B89-D05A-48F0-B0DA-D21598ADDD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4763,7 +4763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4787,6 +4787,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5847,7 +5848,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -8135,7 +8136,7 @@
         <v>38</v>
       </c>
       <c r="E87" t="s">
-        <v>1556</v>
+        <v>11</v>
       </c>
       <c r="F87" t="s">
         <v>11</v>
@@ -8424,7 +8425,7 @@
       <c r="D97" t="s">
         <v>38</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F97" t="s">
@@ -8453,7 +8454,7 @@
       <c r="D98" t="s">
         <v>38</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="9" t="s">
         <v>11</v>
       </c>
       <c r="F98" t="s">
@@ -37584,6 +37585,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010077ADB75EDE6CA24D9907F62E3498CFFE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9e4a933615ec58deeded07da77faa5c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f6c80a7e-4993-4462-a012-3c1269aac47c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dfd25e57b156fdb3c6d899fc66d2ed42" ns2:_="">
     <xsd:import namespace="f6c80a7e-4993-4462-a012-3c1269aac47c"/>
@@ -37721,12 +37728,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
   <ds:schemaRefs>
@@ -37736,6 +37737,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F883CBD-C14F-4597-A1B4-21AD70EB2EF7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37751,13 +37761,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2D5B89-D05A-48F0-B0DA-D21598ADDD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DEF1A2-CF68-46C4-BD12-1437CC11EFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4763,7 +4763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4787,7 +4787,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5265,6 +5264,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I490" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41">
+  <autoFilter ref="A1:I490" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I489">
     <sortCondition ref="A1:A489"/>
   </sortState>
@@ -8425,7 +8425,7 @@
       <c r="D97" t="s">
         <v>38</v>
       </c>
-      <c r="E97" s="9" t="s">
+      <c r="E97" t="s">
         <v>11</v>
       </c>
       <c r="F97" t="s">
@@ -8454,7 +8454,7 @@
       <c r="D98" t="s">
         <v>38</v>
       </c>
-      <c r="E98" s="9" t="s">
+      <c r="E98" t="s">
         <v>11</v>
       </c>
       <c r="F98" t="s">
@@ -12976,7 +12976,7 @@
         <v>73</v>
       </c>
       <c r="E254" t="s">
-        <v>1552</v>
+        <v>11</v>
       </c>
       <c r="F254" t="s">
         <v>39</v>
@@ -37576,21 +37576,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010077ADB75EDE6CA24D9907F62E3498CFFE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9e4a933615ec58deeded07da77faa5c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f6c80a7e-4993-4462-a012-3c1269aac47c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dfd25e57b156fdb3c6d899fc66d2ed42" ns2:_="">
     <xsd:import namespace="f6c80a7e-4993-4462-a012-3c1269aac47c"/>
@@ -37728,24 +37713,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F883CBD-C14F-4597-A1B4-21AD70EB2EF7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37761,4 +37744,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D41B892-0F31-44A1-94C7-240AB508872A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D516A6C-A8B5-4978-87D1-9837FE987C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Segmentos" sheetId="1" r:id="rId1"/>
@@ -4763,7 +4763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4784,10 +4784,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13549,7 +13548,7 @@
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A277" s="9">
+      <c r="A277">
         <v>410312164</v>
       </c>
       <c r="B277" t="s">
@@ -13578,7 +13577,7 @@
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A278" s="9">
+      <c r="A278">
         <v>410312064</v>
       </c>
       <c r="B278" t="s">
@@ -13607,7 +13606,7 @@
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A279" s="9">
+      <c r="A279">
         <v>410310430</v>
       </c>
       <c r="B279" t="s">
@@ -13636,7 +13635,7 @@
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A280" s="9">
+      <c r="A280">
         <v>410310398</v>
       </c>
       <c r="B280" t="s">
@@ -13665,7 +13664,7 @@
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A281" s="9">
+      <c r="A281">
         <v>410310298</v>
       </c>
       <c r="B281" t="s">
@@ -13694,7 +13693,7 @@
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A282" s="9">
+      <c r="A282">
         <v>410310197</v>
       </c>
       <c r="B282" t="s">
@@ -13723,7 +13722,7 @@
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A283" s="9">
+      <c r="A283">
         <v>410310196</v>
       </c>
       <c r="B283" t="s">
@@ -13868,7 +13867,7 @@
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A288" s="9">
+      <c r="A288">
         <v>410290261</v>
       </c>
       <c r="B288" t="s">
@@ -14042,7 +14041,7 @@
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A294" s="9">
+      <c r="A294">
         <v>410270238</v>
       </c>
       <c r="B294" t="s">
@@ -15057,7 +15056,7 @@
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A329" s="9">
+      <c r="A329">
         <v>410121207</v>
       </c>
       <c r="B329" t="s">
@@ -15086,7 +15085,7 @@
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A330" s="9">
+      <c r="A330">
         <v>410121202</v>
       </c>
       <c r="B330" t="s">
@@ -15115,7 +15114,7 @@
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A331" s="9">
+      <c r="A331">
         <v>410121107</v>
       </c>
       <c r="B331" t="s">
@@ -15144,7 +15143,7 @@
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A332" s="9">
+      <c r="A332">
         <v>410121102</v>
       </c>
       <c r="B332" t="s">
@@ -15173,7 +15172,7 @@
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A333" s="9">
+      <c r="A333">
         <v>410120509</v>
       </c>
       <c r="B333" t="s">
@@ -15679,7 +15678,7 @@
         <v>46</v>
       </c>
       <c r="E350" t="s">
-        <v>11</v>
+        <v>1553</v>
       </c>
       <c r="F350" t="s">
         <v>55</v>
@@ -19688,7 +19687,7 @@
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A489" s="9">
+      <c r="A489">
         <v>410010020</v>
       </c>
       <c r="B489" t="s">
@@ -19746,7 +19745,7 @@
       </c>
     </row>
     <row r="491" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A491" s="9">
+      <c r="A491">
         <v>400020031</v>
       </c>
       <c r="B491" t="s">
@@ -19775,7 +19774,7 @@
       </c>
     </row>
     <row r="492" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A492" s="9">
+      <c r="A492">
         <v>400010032</v>
       </c>
       <c r="B492" t="s">
@@ -37635,21 +37634,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010077ADB75EDE6CA24D9907F62E3498CFFE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9e4a933615ec58deeded07da77faa5c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f6c80a7e-4993-4462-a012-3c1269aac47c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dfd25e57b156fdb3c6d899fc66d2ed42" ns2:_="">
     <xsd:import namespace="f6c80a7e-4993-4462-a012-3c1269aac47c"/>
@@ -37787,24 +37771,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F883CBD-C14F-4597-A1B4-21AD70EB2EF7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37820,4 +37802,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D516A6C-A8B5-4978-87D1-9837FE987C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFBD92A4-71EE-4184-8AD2-D3BA72C7B9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6802" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6818" uniqueCount="1560">
   <si>
     <t>PRODUTO</t>
   </si>
@@ -4763,7 +4763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4787,6 +4787,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5263,7 +5265,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I492" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I496" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I492">
     <sortCondition descending="1" ref="A1:A492"/>
   </sortState>
@@ -5623,7 +5625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I492"/>
+  <dimension ref="A1:I496"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -19801,6 +19803,90 @@
       <c r="I492" t="s">
         <v>22</v>
       </c>
+    </row>
+    <row r="493" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A493" s="9">
+        <v>410031912</v>
+      </c>
+      <c r="B493" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C493" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D493" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E493" t="s">
+        <v>11</v>
+      </c>
+      <c r="F493" s="9"/>
+      <c r="G493" s="10"/>
+      <c r="H493" s="10"/>
+      <c r="I493" s="10"/>
+    </row>
+    <row r="494" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A494" s="9">
+        <v>410032511</v>
+      </c>
+      <c r="B494" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C494" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D494" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E494" t="s">
+        <v>11</v>
+      </c>
+      <c r="F494" s="9"/>
+      <c r="G494" s="10"/>
+      <c r="H494" s="10"/>
+      <c r="I494" s="10"/>
+    </row>
+    <row r="495" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A495" s="9">
+        <v>410032209</v>
+      </c>
+      <c r="B495" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C495" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D495" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E495" t="s">
+        <v>11</v>
+      </c>
+      <c r="F495" s="9"/>
+      <c r="G495" s="10"/>
+      <c r="H495" s="10"/>
+      <c r="I495" s="10"/>
+    </row>
+    <row r="496" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A496" s="9">
+        <v>410032012</v>
+      </c>
+      <c r="B496" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C496" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D496" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E496" t="s">
+        <v>11</v>
+      </c>
+      <c r="F496" s="9"/>
+      <c r="G496" s="10"/>
+      <c r="H496" s="10"/>
+      <c r="I496" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A490">
@@ -19836,7 +19922,7 @@
     <cfRule type="duplicateValues" dxfId="3" priority="67"/>
     <cfRule type="duplicateValues" dxfId="2" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A493:A1048576 A1:A490">
+  <conditionalFormatting sqref="A497:A1048576 A1:A490">
     <cfRule type="duplicateValues" dxfId="1" priority="32"/>
     <cfRule type="duplicateValues" dxfId="0" priority="33"/>
   </conditionalFormatting>
@@ -37634,6 +37720,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010077ADB75EDE6CA24D9907F62E3498CFFE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9e4a933615ec58deeded07da77faa5c5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f6c80a7e-4993-4462-a012-3c1269aac47c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dfd25e57b156fdb3c6d899fc66d2ed42" ns2:_="">
     <xsd:import namespace="f6c80a7e-4993-4462-a012-3c1269aac47c"/>
@@ -37771,22 +37872,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F883CBD-C14F-4597-A1B4-21AD70EB2EF7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -37802,21 +37905,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC123CC6-0636-4438-BC6A-1DDA51037C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAE020C-A8D6-469E-92BE-3C02DED247DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6822" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6864" uniqueCount="1560">
   <si>
     <t>PRODUTO</t>
   </si>
@@ -4763,7 +4763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4784,19 +4784,836 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan1" xfId="1" xr:uid="{FE852428-3A3C-4AA6-BBE1-A060037A7EA3}"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="106">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5065,194 +5882,6 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -5267,28 +5896,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I497" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41">
-  <autoFilter ref="A1:I497" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I507" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" headerRowBorderDxfId="15">
+  <autoFilter ref="A1:I507" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I497">
     <sortCondition descending="1" ref="D1:D497"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="33"/>
-    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="105">
   <autoFilter ref="A1:C1272" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E944E400-526F-434F-B83C-CFB22E9A80C5}" name="COD PRODUTO"/>
@@ -5300,12 +5929,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="104" dataDxfId="103">
   <autoFilter ref="A1:C350" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="102"/>
+    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="101"/>
+    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5628,7 +6257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I497"/>
+  <dimension ref="A1:I507"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -6625,7 +7254,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="12">
+      <c r="A35">
         <v>410015092</v>
       </c>
       <c r="B35" t="s">
@@ -12435,7 +13064,7 @@
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A237" s="8">
+      <c r="A237" s="1">
         <v>410252958</v>
       </c>
       <c r="B237" t="s">
@@ -12444,16 +13073,12 @@
       <c r="C237" t="s">
         <v>26</v>
       </c>
-      <c r="D237" s="9" t="s">
+      <c r="D237" t="s">
         <v>27</v>
       </c>
       <c r="E237" t="s">
         <v>16</v>
       </c>
-      <c r="F237" s="9"/>
-      <c r="G237" s="10"/>
-      <c r="H237" s="10"/>
-      <c r="I237" s="10"/>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
@@ -13587,7 +14212,7 @@
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A277" s="11">
+      <c r="A277" s="8">
         <v>430313464</v>
       </c>
       <c r="B277" t="s">
@@ -13616,7 +14241,7 @@
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A278" s="11">
+      <c r="A278" s="8">
         <v>430313462</v>
       </c>
       <c r="B278" t="s">
@@ -13645,7 +14270,7 @@
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A279" s="11">
+      <c r="A279" s="8">
         <v>430313403</v>
       </c>
       <c r="B279" t="s">
@@ -13674,7 +14299,7 @@
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A280" s="11">
+      <c r="A280" s="8">
         <v>430312164</v>
       </c>
       <c r="B280" t="s">
@@ -13703,7 +14328,7 @@
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A281" s="11">
+      <c r="A281" s="8">
         <v>430312103</v>
       </c>
       <c r="B281" t="s">
@@ -13732,7 +14357,7 @@
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A282" s="11">
+      <c r="A282" s="8">
         <v>430312064</v>
       </c>
       <c r="B282" t="s">
@@ -13761,7 +14386,7 @@
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A283" s="11">
+      <c r="A283" s="8">
         <v>430312003</v>
       </c>
       <c r="B283" t="s">
@@ -13906,7 +14531,7 @@
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A288" s="11">
+      <c r="A288" s="8">
         <v>430270138</v>
       </c>
       <c r="B288" t="s">
@@ -14080,7 +14705,7 @@
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A294" s="11">
+      <c r="A294" s="8">
         <v>430251235</v>
       </c>
       <c r="B294" t="s">
@@ -15095,7 +15720,7 @@
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A329" s="11">
+      <c r="A329" s="8">
         <v>430060204</v>
       </c>
       <c r="B329" t="s">
@@ -15124,7 +15749,7 @@
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A330" s="11">
+      <c r="A330" s="8">
         <v>430060104</v>
       </c>
       <c r="B330" t="s">
@@ -15153,7 +15778,7 @@
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A331" s="11">
+      <c r="A331" s="8">
         <v>430043157</v>
       </c>
       <c r="B331" t="s">
@@ -15182,7 +15807,7 @@
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A332" s="11">
+      <c r="A332" s="8">
         <v>430043057</v>
       </c>
       <c r="B332" t="s">
@@ -15211,7 +15836,7 @@
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A333" s="11">
+      <c r="A333" s="8">
         <v>430042957</v>
       </c>
       <c r="B333" t="s">
@@ -15240,7 +15865,7 @@
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A334" s="11">
+      <c r="A334" s="8">
         <v>430041557</v>
       </c>
       <c r="B334" t="s">
@@ -19663,7 +20288,7 @@
       </c>
     </row>
     <row r="489" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A489" s="12">
+      <c r="A489">
         <v>440026410</v>
       </c>
       <c r="B489" t="s">
@@ -19715,7 +20340,7 @@
       </c>
     </row>
     <row r="491" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A491" s="12">
+      <c r="A491">
         <v>440025615</v>
       </c>
       <c r="B491" t="s">
@@ -19741,7 +20366,7 @@
       </c>
     </row>
     <row r="492" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A492" s="12">
+      <c r="A492">
         <v>440015592</v>
       </c>
       <c r="B492" t="s">
@@ -19767,7 +20392,7 @@
       </c>
     </row>
     <row r="493" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A493" s="12">
+      <c r="A493">
         <v>440014792</v>
       </c>
       <c r="B493" t="s">
@@ -19793,7 +20418,7 @@
       </c>
     </row>
     <row r="494" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A494" s="12">
+      <c r="A494">
         <v>440014791</v>
       </c>
       <c r="B494" t="s">
@@ -19819,7 +20444,7 @@
       </c>
     </row>
     <row r="495" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A495" s="12">
+      <c r="A495">
         <v>410050010</v>
       </c>
       <c r="B495" t="s">
@@ -19845,7 +20470,7 @@
       </c>
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A496" s="12">
+      <c r="A496">
         <v>410030503</v>
       </c>
       <c r="B496" t="s">
@@ -19871,7 +20496,7 @@
       </c>
     </row>
     <row r="497" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A497" s="12">
+      <c r="A497">
         <v>410030501</v>
       </c>
       <c r="B497" t="s">
@@ -19896,43 +20521,263 @@
         <v>11</v>
       </c>
     </row>
+    <row r="498" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A498" s="9">
+        <v>430314110</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D498" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E498" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F498" t="s">
+        <v>1558</v>
+      </c>
+      <c r="G498" t="s">
+        <v>1558</v>
+      </c>
+      <c r="H498" t="s">
+        <v>1558</v>
+      </c>
+      <c r="I498" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="499" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A499" s="9">
+        <v>410026323</v>
+      </c>
+      <c r="B499" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C499" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D499" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E499" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F499" s="9"/>
+      <c r="G499" s="11"/>
+      <c r="H499" s="11"/>
+      <c r="I499" s="11"/>
+    </row>
+    <row r="500" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A500" s="9">
+        <v>440010020</v>
+      </c>
+      <c r="B500" t="s">
+        <v>8</v>
+      </c>
+      <c r="C500" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D500" s="9"/>
+      <c r="E500" s="10" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F500" s="9"/>
+      <c r="G500" s="11"/>
+      <c r="H500" s="11"/>
+      <c r="I500" s="11"/>
+    </row>
+    <row r="501" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A501" s="9">
+        <v>410031210</v>
+      </c>
+      <c r="B501" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C501" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D501" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E501" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F501" s="9"/>
+      <c r="G501" s="11"/>
+      <c r="H501" s="11"/>
+      <c r="I501" s="11"/>
+    </row>
+    <row r="502" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A502" s="9">
+        <v>410031810</v>
+      </c>
+      <c r="B502" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C502" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D502" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E502" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F502" s="9"/>
+      <c r="G502" s="11"/>
+      <c r="H502" s="11"/>
+      <c r="I502" s="11"/>
+    </row>
+    <row r="503" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A503" s="9">
+        <v>410032610</v>
+      </c>
+      <c r="B503" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C503" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D503" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E503" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F503" s="9"/>
+      <c r="G503" s="11"/>
+      <c r="H503" s="11"/>
+      <c r="I503" s="11"/>
+    </row>
+    <row r="504" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A504" s="9">
+        <v>430313410</v>
+      </c>
+      <c r="B504" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C504" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D504" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E504" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F504" s="9"/>
+      <c r="G504" s="11"/>
+      <c r="H504" s="11"/>
+      <c r="I504" s="11"/>
+    </row>
+    <row r="505" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A505" s="9">
+        <v>430316910</v>
+      </c>
+      <c r="B505" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C505" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D505" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E505" s="9" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F505" s="9"/>
+      <c r="G505" s="11"/>
+      <c r="H505" s="11"/>
+      <c r="I505" s="11"/>
+    </row>
+    <row r="506" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A506" s="9">
+        <v>440010021</v>
+      </c>
+      <c r="B506" t="s">
+        <v>8</v>
+      </c>
+      <c r="C506" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D506" s="9"/>
+      <c r="E506" s="10" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F506" s="9"/>
+      <c r="G506" s="11"/>
+      <c r="H506" s="11"/>
+      <c r="I506" s="11"/>
+    </row>
+    <row r="507" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A507" s="9">
+        <v>410031010</v>
+      </c>
+      <c r="B507" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C507" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D507" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E507" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F507" s="9"/>
+      <c r="G507" s="11"/>
+      <c r="H507" s="11"/>
+      <c r="I507" s="11"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A490">
-    <cfRule type="duplicateValues" dxfId="24" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A330">
-    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A332">
-    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A333">
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A335:A490">
-    <cfRule type="duplicateValues" dxfId="4" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="70"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A498:A1048576 A1:A490">
-    <cfRule type="duplicateValues" dxfId="1" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  <conditionalFormatting sqref="A508:A1048576 A1:A490">
+    <cfRule type="duplicateValues" dxfId="51" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A507">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -37866,18 +38711,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37899,18 +38744,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAE020C-A8D6-469E-92BE-3C02DED247DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2702D3A2-F88A-4604-9A43-B032BF604029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6864" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6866" uniqueCount="1561">
   <si>
     <t>PRODUTO</t>
   </si>
@@ -4707,6 +4707,9 @@
   </si>
   <si>
     <t>EXPORTAÇÃO</t>
+  </si>
+  <si>
+    <t>SUCRALOSE LIQUIDO</t>
   </si>
 </sst>
 </file>
@@ -4763,7 +4766,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4787,813 +4790,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan1" xfId="1" xr:uid="{FE852428-3A3C-4AA6-BBE1-A060037A7EA3}"/>
   </cellStyles>
-  <dxfs count="106">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5882,6 +5084,194 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -5896,28 +5286,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I507" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" headerRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I507" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43">
   <autoFilter ref="A1:I507" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I497">
     <sortCondition descending="1" ref="D1:D497"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="A1:C1272" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E944E400-526F-434F-B83C-CFB22E9A80C5}" name="COD PRODUTO"/>
@@ -5929,12 +5319,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="104" dataDxfId="103">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="A1:C350" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="102"/>
-    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="101"/>
-    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="100"/>
+    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -20522,7 +19912,7 @@
       </c>
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A498" s="9">
+      <c r="A498">
         <v>430314110</v>
       </c>
       <c r="B498" t="s">
@@ -20551,233 +19941,201 @@
       </c>
     </row>
     <row r="499" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A499" s="9">
+      <c r="A499">
         <v>410026323</v>
       </c>
-      <c r="B499" s="9" t="s">
+      <c r="B499" t="s">
         <v>8</v>
       </c>
-      <c r="C499" s="9" t="s">
+      <c r="C499" t="s">
         <v>9</v>
       </c>
-      <c r="D499" s="9" t="s">
+      <c r="D499" t="s">
         <v>36</v>
       </c>
-      <c r="E499" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F499" s="9"/>
-      <c r="G499" s="11"/>
-      <c r="H499" s="11"/>
-      <c r="I499" s="11"/>
+      <c r="E499" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="500" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A500" s="9">
+      <c r="A500">
         <v>440010020</v>
       </c>
       <c r="B500" t="s">
         <v>8</v>
       </c>
-      <c r="C500" s="9" t="s">
+      <c r="C500" t="s">
         <v>9</v>
       </c>
-      <c r="D500" s="9"/>
-      <c r="E500" s="10" t="s">
+      <c r="D500" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E500" t="s">
         <v>1559</v>
       </c>
-      <c r="F500" s="9"/>
-      <c r="G500" s="11"/>
-      <c r="H500" s="11"/>
-      <c r="I500" s="11"/>
     </row>
     <row r="501" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A501" s="9">
+      <c r="A501">
         <v>410031210</v>
       </c>
-      <c r="B501" s="9" t="s">
+      <c r="B501" t="s">
         <v>38</v>
       </c>
-      <c r="C501" s="9" t="s">
+      <c r="C501" t="s">
         <v>38</v>
       </c>
-      <c r="D501" s="9" t="s">
+      <c r="D501" t="s">
         <v>38</v>
       </c>
-      <c r="E501" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F501" s="9"/>
-      <c r="G501" s="11"/>
-      <c r="H501" s="11"/>
-      <c r="I501" s="11"/>
+      <c r="E501" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A502" s="9">
+      <c r="A502">
         <v>410031810</v>
       </c>
-      <c r="B502" s="9" t="s">
+      <c r="B502" t="s">
         <v>38</v>
       </c>
-      <c r="C502" s="9" t="s">
+      <c r="C502" t="s">
         <v>38</v>
       </c>
-      <c r="D502" s="9" t="s">
+      <c r="D502" t="s">
         <v>38</v>
       </c>
-      <c r="E502" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F502" s="9"/>
-      <c r="G502" s="11"/>
-      <c r="H502" s="11"/>
-      <c r="I502" s="11"/>
+      <c r="E502" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A503" s="9">
+      <c r="A503">
         <v>410032610</v>
       </c>
-      <c r="B503" s="9" t="s">
+      <c r="B503" t="s">
         <v>38</v>
       </c>
-      <c r="C503" s="9" t="s">
+      <c r="C503" t="s">
         <v>38</v>
       </c>
-      <c r="D503" s="9" t="s">
+      <c r="D503" t="s">
         <v>38</v>
       </c>
-      <c r="E503" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F503" s="9"/>
-      <c r="G503" s="11"/>
-      <c r="H503" s="11"/>
-      <c r="I503" s="11"/>
+      <c r="E503" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="504" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A504" s="9">
+      <c r="A504">
         <v>430313410</v>
       </c>
-      <c r="B504" s="9" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C504" s="9" t="s">
-        <v>1558</v>
-      </c>
-      <c r="D504" s="9" t="s">
-        <v>1558</v>
-      </c>
-      <c r="E504" s="9" t="s">
-        <v>1558</v>
-      </c>
-      <c r="F504" s="9"/>
-      <c r="G504" s="11"/>
-      <c r="H504" s="11"/>
-      <c r="I504" s="11"/>
+      <c r="B504" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C504" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D504" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E504" t="s">
+        <v>1558</v>
+      </c>
     </row>
     <row r="505" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A505" s="9">
+      <c r="A505">
         <v>430316910</v>
       </c>
-      <c r="B505" s="9" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C505" s="9" t="s">
-        <v>1558</v>
-      </c>
-      <c r="D505" s="9" t="s">
-        <v>1558</v>
-      </c>
-      <c r="E505" s="9" t="s">
-        <v>1558</v>
-      </c>
-      <c r="F505" s="9"/>
-      <c r="G505" s="11"/>
-      <c r="H505" s="11"/>
-      <c r="I505" s="11"/>
+      <c r="B505" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C505" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D505" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E505" t="s">
+        <v>1558</v>
+      </c>
     </row>
     <row r="506" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A506" s="9">
+      <c r="A506">
         <v>440010021</v>
       </c>
       <c r="B506" t="s">
         <v>8</v>
       </c>
-      <c r="C506" s="9" t="s">
+      <c r="C506" t="s">
         <v>9</v>
       </c>
-      <c r="D506" s="9"/>
-      <c r="E506" s="10" t="s">
+      <c r="D506" t="s">
+        <v>17</v>
+      </c>
+      <c r="E506" t="s">
         <v>1559</v>
       </c>
-      <c r="F506" s="9"/>
-      <c r="G506" s="11"/>
-      <c r="H506" s="11"/>
-      <c r="I506" s="11"/>
     </row>
     <row r="507" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A507" s="9">
+      <c r="A507">
         <v>410031010</v>
       </c>
-      <c r="B507" s="9" t="s">
+      <c r="B507" t="s">
         <v>38</v>
       </c>
-      <c r="C507" s="9" t="s">
+      <c r="C507" t="s">
         <v>38</v>
       </c>
-      <c r="D507" s="9" t="s">
+      <c r="D507" t="s">
         <v>38</v>
       </c>
-      <c r="E507" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F507" s="9"/>
-      <c r="G507" s="11"/>
-      <c r="H507" s="11"/>
-      <c r="I507" s="11"/>
+      <c r="E507" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="26" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A2:A490">
-    <cfRule type="duplicateValues" dxfId="74" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A507">
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A330">
-    <cfRule type="duplicateValues" dxfId="72" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A332">
-    <cfRule type="duplicateValues" dxfId="66" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A333">
-    <cfRule type="duplicateValues" dxfId="60" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A335:A490">
-    <cfRule type="duplicateValues" dxfId="54" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A508:A1048576 A1:A490">
-    <cfRule type="duplicateValues" dxfId="51" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="35"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A507">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -38711,18 +38069,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -38744,18 +38102,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/app/etl/Segmentos.xlsx
+++ b/app/etl/Segmentos.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phillipe.silva\Documents\Nexus\app\etl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2702D3A2-F88A-4604-9A43-B032BF604029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39DD859-7B8D-45CA-BFAB-CE818A6A1216}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Segmentos" sheetId="1" r:id="rId1"/>
-    <sheet name="Tipos" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet name="Padronização-Shelf" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Planilha1" sheetId="4" r:id="rId2"/>
+    <sheet name="Tipos" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="Padronização-Shelf" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6866" uniqueCount="1561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6921" uniqueCount="1573">
   <si>
     <t>PRODUTO</t>
   </si>
@@ -4710,13 +4711,52 @@
   </si>
   <si>
     <t>SUCRALOSE LIQUIDO</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT PACOCA 6X12X35g</t>
+  </si>
+  <si>
+    <t>SEM CATEGORIA</t>
+  </si>
+  <si>
+    <t>Restricao</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT COOKIES CREAM 6X12X35g</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT CHEESECAKE MO 6X12X35g</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT CREME AVELA 6X12X35g</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT BANOFFEE 6X12X20g</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT DOCE DE LEITE 6X12X20g</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT MARACUJA 6X12X20g</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT BROWNIE 6X12X35g</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT TORTA D LIMAO 6X12X35G</t>
+  </si>
+  <si>
+    <t>LINEA HUMMM BARRA PROT BEIJINHO 6X12X20G</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;R$&quot;\ #,##0;[Red]\-&quot;R$&quot;\ #,##0"/>
+  </numFmts>
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4735,13 +4775,79 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="6"/>
+      <color rgb="FF64748B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF334155"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF64748B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF475569"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF059669"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFE11D48"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFE11D48"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="6"/>
+      <color rgb="FFE11D48"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FAFB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -4766,7 +4872,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4790,12 +4896,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan1" xfId="1" xr:uid="{FE852428-3A3C-4AA6-BBE1-A060037A7EA3}"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="46">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4805,6 +4964,204 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <family val="2"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5084,194 +5441,6 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <family val="2"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -5286,28 +5455,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I507" totalsRowShown="0" headerRowDxfId="44" dataDxfId="42" headerRowBorderDxfId="43">
-  <autoFilter ref="A1:I507" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}" name="Tabela1" displayName="Tabela1" ref="A1:I518" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" headerRowBorderDxfId="11">
+  <autoFilter ref="A1:I518" xr:uid="{856D4024-39B1-4F21-91E7-97DCD1EC883E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I497">
     <sortCondition descending="1" ref="D1:D497"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="33"/>
+    <tableColumn id="1" xr3:uid="{C9537D92-D67F-4E2B-9081-ACE090BB5329}" name="PRODUTO" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{B37D3090-3726-496D-B822-F80480572703}" name="BU" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{F938D5A9-8E89-4663-B2AB-9A67BD0A6DD9}" name="CATEGORIA" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{6C809A9A-634F-4015-90AF-0AF9A019F7DF}" name="SEGMENTO" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{FD9C43CC-D37B-41B7-A892-5288742FFF2B}" name="2026" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{2E7929CA-E2F9-47FD-BEC6-CC9CBB29EBAC}" name="2025" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{DEC90D82-5D8C-4314-A3AD-056670C3614E}" name="2024" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{71FA4038-073B-4A82-9919-12E8A98A5555}" name="2023" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{2503E338-9188-40F0-9C1D-4F28B5EBB49A}" name="2022" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}" name="Tabela2" displayName="Tabela2" ref="A1:C1272" totalsRowShown="0" headerRowDxfId="45">
   <autoFilter ref="A1:C1272" xr:uid="{AFFBF06B-9B04-43CD-B211-2430C0023E3A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E944E400-526F-434F-B83C-CFB22E9A80C5}" name="COD PRODUTO"/>
@@ -5319,12 +5488,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}" name="Tabela3" displayName="Tabela3" ref="A1:C350" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43">
   <autoFilter ref="A1:C350" xr:uid="{29635FC4-9EA4-4970-A96C-BA49750380FF}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{3FBD2265-2B43-4619-9DFC-C0D576A04BC6}" name="CÓDIGO" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{9449AEE8-4102-402C-AE0F-72648C160E31}" name="DESCRIÇÃO PROTHEUS" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{1767BAE8-D1C3-41AF-92D0-8BCB97731E90}" name="dias" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5647,7 +5816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I507"/>
+  <dimension ref="A1:I518"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -20093,49 +20262,236 @@
         <v>11</v>
       </c>
     </row>
+    <row r="508" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A508" s="25">
+        <v>440030908</v>
+      </c>
+      <c r="B508" t="s">
+        <v>38</v>
+      </c>
+      <c r="C508" s="26"/>
+      <c r="D508" s="26"/>
+      <c r="E508" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F508" s="26"/>
+      <c r="G508" s="27"/>
+      <c r="H508" s="27"/>
+      <c r="I508" s="27"/>
+    </row>
+    <row r="509" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A509" s="25">
+        <v>440031008</v>
+      </c>
+      <c r="B509" t="s">
+        <v>38</v>
+      </c>
+      <c r="C509" s="26"/>
+      <c r="D509" s="26"/>
+      <c r="E509" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F509" s="26"/>
+      <c r="G509" s="27"/>
+      <c r="H509" s="27"/>
+      <c r="I509" s="27"/>
+    </row>
+    <row r="510" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A510" s="25">
+        <v>440031108</v>
+      </c>
+      <c r="B510" t="s">
+        <v>38</v>
+      </c>
+      <c r="C510" s="26"/>
+      <c r="D510" s="26"/>
+      <c r="E510" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F510" s="26"/>
+      <c r="G510" s="27"/>
+      <c r="H510" s="27"/>
+      <c r="I510" s="27"/>
+    </row>
+    <row r="511" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A511" s="25">
+        <v>440031208</v>
+      </c>
+      <c r="B511" t="s">
+        <v>38</v>
+      </c>
+      <c r="C511" s="26"/>
+      <c r="D511" s="26"/>
+      <c r="E511" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F511" s="26"/>
+      <c r="G511" s="27"/>
+      <c r="H511" s="27"/>
+      <c r="I511" s="27"/>
+    </row>
+    <row r="512" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A512" s="25">
+        <v>440031809</v>
+      </c>
+      <c r="B512" t="s">
+        <v>38</v>
+      </c>
+      <c r="C512" s="26"/>
+      <c r="D512" s="26"/>
+      <c r="E512" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F512" s="26"/>
+      <c r="G512" s="27"/>
+      <c r="H512" s="27"/>
+      <c r="I512" s="27"/>
+    </row>
+    <row r="513" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A513" s="25">
+        <v>440031909</v>
+      </c>
+      <c r="B513" t="s">
+        <v>38</v>
+      </c>
+      <c r="C513" s="26"/>
+      <c r="D513" s="26"/>
+      <c r="E513" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F513" s="26"/>
+      <c r="G513" s="27"/>
+      <c r="H513" s="27"/>
+      <c r="I513" s="27"/>
+    </row>
+    <row r="514" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A514" s="25">
+        <v>440032009</v>
+      </c>
+      <c r="B514" t="s">
+        <v>38</v>
+      </c>
+      <c r="C514" s="26"/>
+      <c r="D514" s="26"/>
+      <c r="E514" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F514" s="26"/>
+      <c r="G514" s="27"/>
+      <c r="H514" s="27"/>
+      <c r="I514" s="27"/>
+    </row>
+    <row r="515" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A515" s="25">
+        <v>440032108</v>
+      </c>
+      <c r="B515" t="s">
+        <v>38</v>
+      </c>
+      <c r="C515" s="26"/>
+      <c r="D515" s="26"/>
+      <c r="E515" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F515" s="26"/>
+      <c r="G515" s="27"/>
+      <c r="H515" s="27"/>
+      <c r="I515" s="27"/>
+    </row>
+    <row r="516" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A516" s="25">
+        <v>440032208</v>
+      </c>
+      <c r="B516" t="s">
+        <v>38</v>
+      </c>
+      <c r="C516" s="26"/>
+      <c r="D516" s="26"/>
+      <c r="E516" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F516" s="26"/>
+      <c r="G516" s="27"/>
+      <c r="H516" s="27"/>
+      <c r="I516" s="27"/>
+    </row>
+    <row r="517" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A517" s="25">
+        <v>440032509</v>
+      </c>
+      <c r="B517" t="s">
+        <v>38</v>
+      </c>
+      <c r="C517" s="26"/>
+      <c r="D517" s="26"/>
+      <c r="E517" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F517" s="26"/>
+      <c r="G517" s="27"/>
+      <c r="H517" s="27"/>
+      <c r="I517" s="27"/>
+    </row>
+    <row r="518" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A518" s="28">
+        <v>440032609</v>
+      </c>
+      <c r="B518" t="s">
+        <v>38</v>
+      </c>
+      <c r="C518" s="28"/>
+      <c r="D518" s="28"/>
+      <c r="E518" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F518" s="28"/>
+      <c r="G518" s="29"/>
+      <c r="H518" s="29"/>
+      <c r="I518" s="29"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A490">
-    <cfRule type="duplicateValues" dxfId="25" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="110"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A507">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+  <conditionalFormatting sqref="A2:A518">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A330">
-    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A332">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A333">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A335:A490">
-    <cfRule type="duplicateValues" dxfId="4" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A508:A1048576 A1:A490">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="35"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -20146,6 +20502,302 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D83C283-E3A7-46A3-89C0-FF792AC5135D}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="9">
+        <v>440030908</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D1" s="12">
+        <v>403</v>
+      </c>
+      <c r="E1" s="13">
+        <v>0</v>
+      </c>
+      <c r="F1" s="14">
+        <v>0</v>
+      </c>
+      <c r="G1" s="15">
+        <v>0</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
+        <v>440031008</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>1564</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D2" s="20">
+        <v>441</v>
+      </c>
+      <c r="E2" s="21">
+        <v>0</v>
+      </c>
+      <c r="F2" s="22">
+        <v>0</v>
+      </c>
+      <c r="G2" s="23">
+        <v>0</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>440031108</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D3" s="12">
+        <v>441</v>
+      </c>
+      <c r="E3" s="13">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14">
+        <v>0</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="17">
+        <v>440031208</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D4" s="20">
+        <v>412</v>
+      </c>
+      <c r="E4" s="21">
+        <v>0</v>
+      </c>
+      <c r="F4" s="22">
+        <v>0</v>
+      </c>
+      <c r="G4" s="23">
+        <v>0</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>440031809</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D5" s="12">
+        <v>216</v>
+      </c>
+      <c r="E5" s="13">
+        <v>0</v>
+      </c>
+      <c r="F5" s="14">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="17">
+        <v>440031909</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D6" s="20">
+        <v>214</v>
+      </c>
+      <c r="E6" s="21">
+        <v>0</v>
+      </c>
+      <c r="F6" s="22">
+        <v>0</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>440032009</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D7" s="12">
+        <v>277</v>
+      </c>
+      <c r="E7" s="13">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="G7" s="15">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="17">
+        <v>440032108</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D8" s="20">
+        <v>837</v>
+      </c>
+      <c r="E8" s="21">
+        <v>0</v>
+      </c>
+      <c r="F8" s="22">
+        <v>0</v>
+      </c>
+      <c r="G8" s="23">
+        <v>0</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>440032208</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D9" s="12">
+        <v>488</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="17">
+        <v>440032509</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D10" s="20">
+        <v>170</v>
+      </c>
+      <c r="E10" s="21">
+        <v>0</v>
+      </c>
+      <c r="F10" s="22">
+        <v>0</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>440032609</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>1572</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D11" s="12">
+        <v>278</v>
+      </c>
+      <c r="E11" s="13">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="15">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02BEBDC4-8518-4725-9A6E-F3F5ED578538}">
   <dimension ref="A1:C1272"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -34155,7 +34807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB8DDEA0-3BF0-48F1-BAE3-4AA1DE0143BB}">
   <dimension ref="A1:C350"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -38069,18 +38721,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -38102,18 +38754,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1F20546-7FB8-473C-993C-8D239BFE1C6F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA0CA206-730C-405E-B545-6F223619D12E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>